--- a/RAMON FRANCO/Junio/GASTOS_RAMON FRANCO_JUNIO.xlsx
+++ b/RAMON FRANCO/Junio/GASTOS_RAMON FRANCO_JUNIO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\RAMON FRANCO\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{358324FE-247C-4BE8-94A9-5CEA5C37B878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{950FFAB5-D576-4A17-B185-EBF6373D7DCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="52">
   <si>
     <t>Domicilio:</t>
   </si>
@@ -163,9 +163,6 @@
   </si>
   <si>
     <t>Prevision Extraordinaria</t>
-  </si>
-  <si>
-    <t>Doartero -  Reparacion de puerta principal</t>
   </si>
   <si>
     <t>PERIODO: JUNIO - Vto. 14/07</t>
@@ -198,7 +195,7 @@
     <numFmt numFmtId="165" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
     <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -291,6 +288,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -488,7 +493,7 @@
     <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -581,8 +586,6 @@
     <xf numFmtId="0" fontId="8" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="7" fillId="5" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -667,6 +670,11 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="12" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="12" fillId="8" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="13" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -1039,10 +1047,10 @@
       <c r="D3" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="73">
+      <c r="E3" s="71">
         <v>1153202676</v>
       </c>
-      <c r="F3" s="73"/>
+      <c r="F3" s="71"/>
       <c r="H3" s="6"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1074,7 +1082,7 @@
       <c r="C7" s="10"/>
       <c r="D7" s="10"/>
       <c r="E7" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F7" s="10"/>
       <c r="G7" s="11"/>
@@ -1119,16 +1127,16 @@
       <c r="H11" s="8"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="83" t="s">
+      <c r="A12" s="81" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="83"/>
-      <c r="C12" s="83"/>
-      <c r="D12" s="83"/>
-      <c r="E12" s="83"/>
-      <c r="F12" s="83"/>
-      <c r="G12" s="83"/>
-      <c r="H12" s="83"/>
+      <c r="B12" s="81"/>
+      <c r="C12" s="81"/>
+      <c r="D12" s="81"/>
+      <c r="E12" s="81"/>
+      <c r="F12" s="81"/>
+      <c r="G12" s="81"/>
+      <c r="H12" s="81"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="18"/>
@@ -1169,7 +1177,7 @@
       <c r="E15" s="19"/>
       <c r="F15" s="19"/>
       <c r="G15" s="19"/>
-      <c r="H15" s="63">
+      <c r="H15" s="98">
         <v>8379</v>
       </c>
     </row>
@@ -1209,16 +1217,16 @@
       <c r="H18" s="52"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="84" t="s">
+      <c r="A19" s="82" t="s">
         <v>8</v>
       </c>
-      <c r="B19" s="85"/>
-      <c r="C19" s="85"/>
-      <c r="D19" s="85"/>
-      <c r="E19" s="85"/>
-      <c r="F19" s="85"/>
-      <c r="G19" s="85"/>
-      <c r="H19" s="86"/>
+      <c r="B19" s="83"/>
+      <c r="C19" s="83"/>
+      <c r="D19" s="83"/>
+      <c r="E19" s="83"/>
+      <c r="F19" s="83"/>
+      <c r="G19" s="83"/>
+      <c r="H19" s="84"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="18" t="s">
@@ -1260,16 +1268,16 @@
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="84" t="s">
+      <c r="A23" s="82" t="s">
         <v>18</v>
       </c>
-      <c r="B23" s="85"/>
-      <c r="C23" s="85"/>
-      <c r="D23" s="85"/>
-      <c r="E23" s="85"/>
-      <c r="F23" s="85"/>
-      <c r="G23" s="85"/>
-      <c r="H23" s="86"/>
+      <c r="B23" s="83"/>
+      <c r="C23" s="83"/>
+      <c r="D23" s="83"/>
+      <c r="E23" s="83"/>
+      <c r="F23" s="83"/>
+      <c r="G23" s="83"/>
+      <c r="H23" s="84"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="28" t="s">
@@ -1285,7 +1293,7 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="18" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B25" s="19"/>
       <c r="C25" s="19"/>
@@ -1311,20 +1319,20 @@
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="87" t="s">
+      <c r="A27" s="85" t="s">
         <v>20</v>
       </c>
-      <c r="B27" s="87"/>
-      <c r="C27" s="87"/>
-      <c r="D27" s="87"/>
-      <c r="E27" s="87"/>
-      <c r="F27" s="87"/>
-      <c r="G27" s="87"/>
-      <c r="H27" s="87"/>
+      <c r="B27" s="85"/>
+      <c r="C27" s="85"/>
+      <c r="D27" s="85"/>
+      <c r="E27" s="85"/>
+      <c r="F27" s="85"/>
+      <c r="G27" s="85"/>
+      <c r="H27" s="85"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B28" s="19"/>
       <c r="C28" s="19"/>
@@ -1354,8 +1362,8 @@
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="28" t="s">
-        <v>45</v>
+      <c r="A30" s="96" t="s">
+        <v>30</v>
       </c>
       <c r="B30" s="19"/>
       <c r="C30" s="25"/>
@@ -1363,18 +1371,18 @@
       <c r="E30" s="59"/>
       <c r="F30" s="19"/>
       <c r="G30" s="19"/>
-      <c r="H30" s="26">
-        <v>110000</v>
+      <c r="H30" s="97">
+        <v>266100</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="70"/>
-      <c r="B31" s="71"/>
-      <c r="C31" s="71"/>
-      <c r="D31" s="71"/>
-      <c r="E31" s="71"/>
-      <c r="F31" s="71"/>
-      <c r="G31" s="71"/>
+      <c r="A31" s="68"/>
+      <c r="B31" s="69"/>
+      <c r="C31" s="69"/>
+      <c r="D31" s="69"/>
+      <c r="E31" s="69"/>
+      <c r="F31" s="69"/>
+      <c r="G31" s="69"/>
       <c r="H31" s="26"/>
       <c r="K31" s="53"/>
       <c r="L31" t="s">
@@ -1393,23 +1401,23 @@
       <c r="G32" s="22"/>
       <c r="H32" s="27">
         <f>SUM(H28:H31)</f>
-        <v>220430.94</v>
+        <v>376530.94</v>
       </c>
       <c r="L32" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" s="84" t="s">
+      <c r="A33" s="82" t="s">
         <v>21</v>
       </c>
-      <c r="B33" s="85"/>
-      <c r="C33" s="85"/>
-      <c r="D33" s="85"/>
-      <c r="E33" s="85"/>
-      <c r="F33" s="85"/>
-      <c r="G33" s="85"/>
-      <c r="H33" s="86"/>
+      <c r="B33" s="83"/>
+      <c r="C33" s="83"/>
+      <c r="D33" s="83"/>
+      <c r="E33" s="83"/>
+      <c r="F33" s="83"/>
+      <c r="G33" s="83"/>
+      <c r="H33" s="84"/>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
@@ -1428,7 +1436,7 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="21" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B35" s="22"/>
       <c r="C35" s="22"/>
@@ -1436,7 +1444,7 @@
       <c r="E35" s="22"/>
       <c r="F35" s="22"/>
       <c r="G35" s="22"/>
-      <c r="H35" s="68">
+      <c r="H35" s="100">
         <v>134182.76</v>
       </c>
       <c r="I35" s="53"/>
@@ -1455,16 +1463,16 @@
       <c r="H36" s="32"/>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A37" s="84" t="s">
+      <c r="A37" s="82" t="s">
         <v>22</v>
       </c>
-      <c r="B37" s="85"/>
-      <c r="C37" s="85"/>
-      <c r="D37" s="85"/>
-      <c r="E37" s="85"/>
-      <c r="F37" s="85"/>
-      <c r="G37" s="85"/>
-      <c r="H37" s="86"/>
+      <c r="B37" s="83"/>
+      <c r="C37" s="83"/>
+      <c r="D37" s="83"/>
+      <c r="E37" s="83"/>
+      <c r="F37" s="83"/>
+      <c r="G37" s="83"/>
+      <c r="H37" s="84"/>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="60" t="s">
@@ -1476,7 +1484,7 @@
       <c r="E38" s="61"/>
       <c r="F38" s="61"/>
       <c r="G38" s="61"/>
-      <c r="H38" s="69">
+      <c r="H38" s="99">
         <v>47532.32</v>
       </c>
     </row>
@@ -1492,7 +1500,7 @@
       <c r="G39" s="34"/>
       <c r="H39" s="35">
         <f>H17+H22+H26+H32+H35+H38</f>
-        <v>700767.65</v>
+        <v>856867.65</v>
       </c>
       <c r="I39" s="62"/>
     </row>
@@ -1509,71 +1517,71 @@
       <c r="H40" s="57"/>
     </row>
     <row r="41" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="74" t="s">
+      <c r="A41" s="72" t="s">
         <v>14</v>
       </c>
-      <c r="B41" s="75"/>
-      <c r="C41" s="75"/>
-      <c r="D41" s="75"/>
-      <c r="E41" s="75"/>
-      <c r="F41" s="75"/>
-      <c r="G41" s="75"/>
-      <c r="H41" s="76"/>
+      <c r="B41" s="73"/>
+      <c r="C41" s="73"/>
+      <c r="D41" s="73"/>
+      <c r="E41" s="73"/>
+      <c r="F41" s="73"/>
+      <c r="G41" s="73"/>
+      <c r="H41" s="74"/>
     </row>
     <row r="42" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="77"/>
-      <c r="B42" s="78"/>
-      <c r="C42" s="78"/>
-      <c r="D42" s="78"/>
-      <c r="E42" s="78"/>
-      <c r="F42" s="78"/>
-      <c r="G42" s="78"/>
-      <c r="H42" s="79"/>
+      <c r="A42" s="75"/>
+      <c r="B42" s="76"/>
+      <c r="C42" s="76"/>
+      <c r="D42" s="76"/>
+      <c r="E42" s="76"/>
+      <c r="F42" s="76"/>
+      <c r="G42" s="76"/>
+      <c r="H42" s="77"/>
     </row>
     <row r="43" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="70" t="s">
+      <c r="A43" s="68" t="s">
         <v>43</v>
       </c>
-      <c r="B43" s="71"/>
-      <c r="C43" s="71"/>
-      <c r="D43" s="71"/>
-      <c r="E43" s="71"/>
-      <c r="F43" s="71"/>
-      <c r="G43" s="71"/>
+      <c r="B43" s="69"/>
+      <c r="C43" s="69"/>
+      <c r="D43" s="69"/>
+      <c r="E43" s="69"/>
+      <c r="F43" s="69"/>
+      <c r="G43" s="69"/>
       <c r="H43" s="36">
         <v>420000</v>
       </c>
     </row>
     <row r="44" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="94"/>
-      <c r="B44" s="95"/>
-      <c r="C44" s="95"/>
-      <c r="D44" s="95"/>
-      <c r="E44" s="95"/>
-      <c r="F44" s="95"/>
-      <c r="G44" s="96"/>
+      <c r="A44" s="92"/>
+      <c r="B44" s="93"/>
+      <c r="C44" s="93"/>
+      <c r="D44" s="93"/>
+      <c r="E44" s="93"/>
+      <c r="F44" s="93"/>
+      <c r="G44" s="94"/>
       <c r="H44" s="36"/>
     </row>
     <row r="45" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="88"/>
-      <c r="B45" s="89"/>
-      <c r="C45" s="89"/>
-      <c r="D45" s="89"/>
-      <c r="E45" s="89"/>
-      <c r="F45" s="89"/>
-      <c r="G45" s="90"/>
+      <c r="A45" s="86"/>
+      <c r="B45" s="87"/>
+      <c r="C45" s="87"/>
+      <c r="D45" s="87"/>
+      <c r="E45" s="87"/>
+      <c r="F45" s="87"/>
+      <c r="G45" s="88"/>
       <c r="H45" s="36"/>
     </row>
     <row r="46" spans="1:11" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="91" t="s">
+      <c r="A46" s="89" t="s">
         <v>29</v>
       </c>
-      <c r="B46" s="92"/>
-      <c r="C46" s="92"/>
-      <c r="D46" s="92"/>
-      <c r="E46" s="92"/>
-      <c r="F46" s="92"/>
-      <c r="G46" s="93"/>
+      <c r="B46" s="90"/>
+      <c r="C46" s="90"/>
+      <c r="D46" s="90"/>
+      <c r="E46" s="90"/>
+      <c r="F46" s="90"/>
+      <c r="G46" s="91"/>
       <c r="H46" s="37">
         <f>SUM(H43:H45)</f>
         <v>420000</v>
@@ -1613,18 +1621,18 @@
       <c r="J49" s="15"/>
     </row>
     <row r="50" spans="1:10" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="97" t="s">
+      <c r="A50" s="95" t="s">
         <v>37</v>
       </c>
-      <c r="B50" s="97"/>
-      <c r="C50" s="97"/>
-      <c r="D50" s="97"/>
-      <c r="E50" s="97"/>
-      <c r="F50" s="97"/>
-      <c r="G50" s="97"/>
+      <c r="B50" s="95"/>
+      <c r="C50" s="95"/>
+      <c r="D50" s="95"/>
+      <c r="E50" s="95"/>
+      <c r="F50" s="95"/>
+      <c r="G50" s="95"/>
       <c r="H50" s="35">
         <f>+H39+H40</f>
-        <v>700767.65</v>
+        <v>856867.65</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1673,16 +1681,16 @@
       <c r="H54" s="19"/>
     </row>
     <row r="55" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A55" s="80" t="s">
+      <c r="A55" s="78" t="s">
         <v>15</v>
       </c>
-      <c r="B55" s="81"/>
-      <c r="C55" s="81"/>
-      <c r="D55" s="81"/>
-      <c r="E55" s="81"/>
-      <c r="F55" s="81"/>
-      <c r="G55" s="81"/>
-      <c r="H55" s="82"/>
+      <c r="B55" s="79"/>
+      <c r="C55" s="79"/>
+      <c r="D55" s="79"/>
+      <c r="E55" s="79"/>
+      <c r="F55" s="79"/>
+      <c r="G55" s="79"/>
+      <c r="H55" s="80"/>
     </row>
     <row r="56" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A56" s="41" t="s">
@@ -1700,7 +1708,7 @@
     </row>
     <row r="57" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="43" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B57" s="44"/>
       <c r="C57" s="44"/>
@@ -1736,7 +1744,7 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B60" s="44"/>
       <c r="C60" s="44"/>
@@ -1746,7 +1754,7 @@
       <c r="G60" s="44"/>
       <c r="H60" s="45">
         <f>-(H39+H53)</f>
-        <v>-1120767.6499999999</v>
+        <v>-1276867.6499999999</v>
       </c>
       <c r="J60" s="15"/>
     </row>
@@ -1762,74 +1770,74 @@
       <c r="G61" s="47"/>
       <c r="H61" s="58">
         <f>SUM(H56:H60)</f>
-        <v>471114.10188048007</v>
+        <v>315014.10188048007</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B63" s="72" t="s">
-        <v>50</v>
-      </c>
-      <c r="C63" s="72"/>
-      <c r="D63" s="72"/>
-      <c r="E63" s="72"/>
-      <c r="F63" s="72"/>
-      <c r="G63" s="72"/>
+      <c r="B63" s="70" t="s">
+        <v>49</v>
+      </c>
+      <c r="C63" s="70"/>
+      <c r="D63" s="70"/>
+      <c r="E63" s="70"/>
+      <c r="F63" s="70"/>
+      <c r="G63" s="70"/>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B64" s="72"/>
-      <c r="C64" s="72"/>
-      <c r="D64" s="72"/>
-      <c r="E64" s="72"/>
-      <c r="F64" s="72"/>
-      <c r="G64" s="72"/>
+      <c r="B64" s="70"/>
+      <c r="C64" s="70"/>
+      <c r="D64" s="70"/>
+      <c r="E64" s="70"/>
+      <c r="F64" s="70"/>
+      <c r="G64" s="70"/>
     </row>
     <row r="65" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B65" s="72"/>
-      <c r="C65" s="72"/>
-      <c r="D65" s="72"/>
-      <c r="E65" s="72"/>
-      <c r="F65" s="72"/>
-      <c r="G65" s="72"/>
+      <c r="B65" s="70"/>
+      <c r="C65" s="70"/>
+      <c r="D65" s="70"/>
+      <c r="E65" s="70"/>
+      <c r="F65" s="70"/>
+      <c r="G65" s="70"/>
     </row>
     <row r="66" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B66" s="72"/>
-      <c r="C66" s="72"/>
-      <c r="D66" s="72"/>
-      <c r="E66" s="72"/>
-      <c r="F66" s="72"/>
-      <c r="G66" s="72"/>
+      <c r="B66" s="70"/>
+      <c r="C66" s="70"/>
+      <c r="D66" s="70"/>
+      <c r="E66" s="70"/>
+      <c r="F66" s="70"/>
+      <c r="G66" s="70"/>
     </row>
     <row r="67" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B67" s="72"/>
-      <c r="C67" s="72"/>
-      <c r="D67" s="72"/>
-      <c r="E67" s="72"/>
-      <c r="F67" s="72"/>
-      <c r="G67" s="72"/>
+      <c r="B67" s="70"/>
+      <c r="C67" s="70"/>
+      <c r="D67" s="70"/>
+      <c r="E67" s="70"/>
+      <c r="F67" s="70"/>
+      <c r="G67" s="70"/>
     </row>
     <row r="68" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B68" s="72"/>
-      <c r="C68" s="72"/>
-      <c r="D68" s="72"/>
-      <c r="E68" s="72"/>
-      <c r="F68" s="72"/>
-      <c r="G68" s="72"/>
+      <c r="B68" s="70"/>
+      <c r="C68" s="70"/>
+      <c r="D68" s="70"/>
+      <c r="E68" s="70"/>
+      <c r="F68" s="70"/>
+      <c r="G68" s="70"/>
     </row>
     <row r="69" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B69" s="72"/>
-      <c r="C69" s="72"/>
-      <c r="D69" s="72"/>
-      <c r="E69" s="72"/>
-      <c r="F69" s="72"/>
-      <c r="G69" s="72"/>
+      <c r="B69" s="70"/>
+      <c r="C69" s="70"/>
+      <c r="D69" s="70"/>
+      <c r="E69" s="70"/>
+      <c r="F69" s="70"/>
+      <c r="G69" s="70"/>
     </row>
     <row r="70" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B70" s="72"/>
-      <c r="C70" s="72"/>
-      <c r="D70" s="72"/>
-      <c r="E70" s="72"/>
-      <c r="F70" s="72"/>
-      <c r="G70" s="72"/>
+      <c r="B70" s="70"/>
+      <c r="C70" s="70"/>
+      <c r="D70" s="70"/>
+      <c r="E70" s="70"/>
+      <c r="F70" s="70"/>
+      <c r="G70" s="70"/>
     </row>
   </sheetData>
   <mergeCells count="16">

--- a/RAMON FRANCO/Junio/GASTOS_RAMON FRANCO_JUNIO.xlsx
+++ b/RAMON FRANCO/Junio/GASTOS_RAMON FRANCO_JUNIO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\RAMON FRANCO\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{950FFAB5-D576-4A17-B185-EBF6373D7DCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D854767A-EB65-4E5B-8E43-C1684968E7D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Hoja1!$A$1:$H$71</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Hoja1!$A$1:$H$72</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="55">
   <si>
     <t>Domicilio:</t>
   </si>
@@ -156,12 +156,6 @@
     <t>son 74897$ que recuperamos con el abono de ascensores</t>
   </si>
   <si>
-    <t>Salvatierra Matias - Desobstruccion 3B</t>
-  </si>
-  <si>
-    <t>Arreglo sala de ascensores - Colocacion de ventana</t>
-  </si>
-  <si>
     <t>Prevision Extraordinaria</t>
   </si>
   <si>
@@ -184,6 +178,21 @@
   </si>
   <si>
     <t>Egresos gastos del mes - MAYO</t>
+  </si>
+  <si>
+    <t>SAC</t>
+  </si>
+  <si>
+    <t>Kromacolor compra de recuplast teja 10lts</t>
+  </si>
+  <si>
+    <t>Techos 25 de Mayo compra membrana de aluminio y silicona</t>
+  </si>
+  <si>
+    <t>Herrero soldadura puerta medidores</t>
+  </si>
+  <si>
+    <t>Mano de obra terraza Sr. Leonardo Balcazza</t>
   </si>
 </sst>
 </file>
@@ -195,7 +204,7 @@
     <numFmt numFmtId="165" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
     <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -288,14 +297,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -493,7 +494,7 @@
     <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -670,11 +671,8 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="12" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="12" fillId="8" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="13" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="8" fillId="4" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="7" fillId="5" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -1012,7 +1010,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L70"/>
+  <dimension ref="A1:L71"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
@@ -1082,7 +1080,7 @@
       <c r="C7" s="10"/>
       <c r="D7" s="10"/>
       <c r="E7" s="10" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F7" s="10"/>
       <c r="G7" s="11"/>
@@ -1165,205 +1163,203 @@
         <v>266091</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="B15" s="19"/>
       <c r="C15" s="19"/>
-      <c r="D15" s="19" t="s">
-        <v>32</v>
-      </c>
+      <c r="D15" s="19"/>
       <c r="E15" s="19"/>
       <c r="F15" s="19"/>
       <c r="G15" s="19"/>
-      <c r="H15" s="98">
-        <v>8379</v>
+      <c r="H15" s="63">
+        <f>H14/2</f>
+        <v>133045.5</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="18"/>
+      <c r="A16" s="18" t="s">
+        <v>31</v>
+      </c>
       <c r="B16" s="19"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="19"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19" t="s">
+        <v>32</v>
+      </c>
       <c r="E16" s="19"/>
       <c r="F16" s="19"/>
       <c r="G16" s="19"/>
-      <c r="H16" s="63"/>
+      <c r="H16" s="63">
+        <v>8379</v>
+      </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="21" t="s">
+      <c r="A17" s="18"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="63"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B17" s="22"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="22"/>
-      <c r="H17" s="51">
-        <f>SUM(H13:H16)</f>
-        <v>274470</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="23"/>
-      <c r="B18" s="24"/>
-      <c r="C18" s="24"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="24"/>
-      <c r="G18" s="24"/>
-      <c r="H18" s="52"/>
+      <c r="B18" s="22"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="51">
+        <f>SUM(H13:H17)</f>
+        <v>407515.5</v>
+      </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="82" t="s">
+      <c r="A19" s="23"/>
+      <c r="B19" s="24"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="24"/>
+      <c r="H19" s="52"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" s="82" t="s">
         <v>8</v>
       </c>
-      <c r="B19" s="83"/>
-      <c r="C19" s="83"/>
-      <c r="D19" s="83"/>
-      <c r="E19" s="83"/>
-      <c r="F19" s="83"/>
-      <c r="G19" s="83"/>
-      <c r="H19" s="84"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="18" t="s">
+      <c r="B20" s="83"/>
+      <c r="C20" s="83"/>
+      <c r="D20" s="83"/>
+      <c r="E20" s="83"/>
+      <c r="F20" s="83"/>
+      <c r="G20" s="83"/>
+      <c r="H20" s="84"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="B20" s="19"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="19"/>
-      <c r="H20" s="30">
-        <v>24151.63</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="18"/>
       <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
+      <c r="C21" s="25"/>
       <c r="D21" s="19"/>
-      <c r="E21" s="25"/>
+      <c r="E21" s="19"/>
       <c r="F21" s="19"/>
       <c r="G21" s="19"/>
-      <c r="H21" s="26"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="21" t="s">
+      <c r="H21" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="18"/>
+      <c r="B22" s="19"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="26"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="B22" s="22"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="27">
-        <f>SUM(H20:H21)</f>
-        <v>24151.63</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="82" t="s">
+      <c r="B23" s="22"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="27">
+        <f>SUM(H21:H22)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" s="82" t="s">
         <v>18</v>
       </c>
-      <c r="B23" s="83"/>
-      <c r="C23" s="83"/>
-      <c r="D23" s="83"/>
-      <c r="E23" s="83"/>
-      <c r="F23" s="83"/>
-      <c r="G23" s="83"/>
-      <c r="H23" s="84"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="28" t="s">
+      <c r="B24" s="83"/>
+      <c r="C24" s="83"/>
+      <c r="D24" s="83"/>
+      <c r="E24" s="83"/>
+      <c r="F24" s="83"/>
+      <c r="G24" s="83"/>
+      <c r="H24" s="84"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="B24" s="29"/>
-      <c r="C24" s="29"/>
-      <c r="D24" s="29"/>
-      <c r="E24" s="29"/>
-      <c r="F24" s="29"/>
-      <c r="G24" s="29"/>
-      <c r="H24" s="30"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="B25" s="19"/>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="26"/>
+      <c r="B25" s="29"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="29"/>
+      <c r="E25" s="29"/>
+      <c r="F25" s="29"/>
+      <c r="G25" s="29"/>
+      <c r="H25" s="30"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="21" t="s">
+      <c r="A26" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="26"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B26" s="22"/>
-      <c r="C26" s="22"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="22"/>
-      <c r="F26" s="22"/>
-      <c r="G26" s="22"/>
-      <c r="H26" s="27">
-        <f>SUM(H24:H25)</f>
+      <c r="B27" s="22"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="22"/>
+      <c r="H27" s="27">
+        <f>SUM(H25:H26)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="85" t="s">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" s="85" t="s">
         <v>20</v>
       </c>
-      <c r="B27" s="85"/>
-      <c r="C27" s="85"/>
-      <c r="D27" s="85"/>
-      <c r="E27" s="85"/>
-      <c r="F27" s="85"/>
-      <c r="G27" s="85"/>
-      <c r="H27" s="85"/>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="B28" s="19"/>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19"/>
-      <c r="H28" s="26">
-        <v>91930.94</v>
-      </c>
+      <c r="B28" s="85"/>
+      <c r="C28" s="85"/>
+      <c r="D28" s="85"/>
+      <c r="E28" s="85"/>
+      <c r="F28" s="85"/>
+      <c r="G28" s="85"/>
+      <c r="H28" s="85"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" s="28" t="s">
-        <v>42</v>
+      <c r="A29" s="18" t="s">
+        <v>45</v>
       </c>
       <c r="B29" s="19"/>
-      <c r="C29" s="25"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="59"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
       <c r="F29" s="19"/>
       <c r="G29" s="19"/>
       <c r="H29" s="26">
-        <v>18500</v>
-      </c>
-      <c r="K29">
-        <v>89897</v>
+        <v>70000</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="96" t="s">
-        <v>30</v>
+      <c r="A30" s="28" t="s">
+        <v>51</v>
       </c>
       <c r="B30" s="19"/>
       <c r="C30" s="25"/>
@@ -1371,369 +1367,380 @@
       <c r="E30" s="59"/>
       <c r="F30" s="19"/>
       <c r="G30" s="19"/>
-      <c r="H30" s="97">
-        <v>266100</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="68"/>
-      <c r="B31" s="69"/>
-      <c r="C31" s="69"/>
-      <c r="D31" s="69"/>
-      <c r="E31" s="69"/>
-      <c r="F31" s="69"/>
-      <c r="G31" s="69"/>
-      <c r="H31" s="26"/>
-      <c r="K31" s="53"/>
-      <c r="L31" t="s">
+      <c r="H30" s="26">
+        <v>75335</v>
+      </c>
+      <c r="K30">
+        <v>89897</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="B31" s="19"/>
+      <c r="C31" s="25"/>
+      <c r="D31" s="29"/>
+      <c r="E31" s="59"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="26">
+        <v>85000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="68" t="s">
+        <v>52</v>
+      </c>
+      <c r="B32" s="69"/>
+      <c r="C32" s="69"/>
+      <c r="D32" s="69"/>
+      <c r="E32" s="69"/>
+      <c r="F32" s="69"/>
+      <c r="G32" s="69"/>
+      <c r="H32" s="26">
+        <v>94500</v>
+      </c>
+      <c r="K32" s="53"/>
+      <c r="L32" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32" s="21" t="s">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="B32" s="22"/>
-      <c r="C32" s="22"/>
-      <c r="D32" s="22"/>
-      <c r="E32" s="22"/>
-      <c r="F32" s="22"/>
-      <c r="G32" s="22"/>
-      <c r="H32" s="27">
-        <f>SUM(H28:H31)</f>
-        <v>376530.94</v>
-      </c>
-      <c r="L32" t="s">
+      <c r="B33" s="22"/>
+      <c r="C33" s="22"/>
+      <c r="D33" s="22"/>
+      <c r="E33" s="22"/>
+      <c r="F33" s="22"/>
+      <c r="G33" s="22"/>
+      <c r="H33" s="27">
+        <f>SUM(H29:H32)</f>
+        <v>324835</v>
+      </c>
+      <c r="L33" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" s="82" t="s">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A34" s="82" t="s">
         <v>21</v>
       </c>
-      <c r="B33" s="83"/>
-      <c r="C33" s="83"/>
-      <c r="D33" s="83"/>
-      <c r="E33" s="83"/>
-      <c r="F33" s="83"/>
-      <c r="G33" s="83"/>
-      <c r="H33" s="84"/>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34" s="18" t="s">
+      <c r="B34" s="83"/>
+      <c r="C34" s="83"/>
+      <c r="D34" s="83"/>
+      <c r="E34" s="83"/>
+      <c r="F34" s="83"/>
+      <c r="G34" s="83"/>
+      <c r="H34" s="84"/>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A35" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B34" s="19"/>
-      <c r="C34" s="19" t="s">
+      <c r="B35" s="19"/>
+      <c r="C35" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="19"/>
-      <c r="H34" s="31"/>
-      <c r="I34" s="53"/>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35" s="21" t="s">
+      <c r="D35" s="19"/>
+      <c r="E35" s="19"/>
+      <c r="F35" s="19"/>
+      <c r="G35" s="19"/>
+      <c r="H35" s="31"/>
+      <c r="I35" s="53"/>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A36" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="B36" s="22"/>
+      <c r="C36" s="22"/>
+      <c r="D36" s="22"/>
+      <c r="E36" s="22"/>
+      <c r="F36" s="22"/>
+      <c r="G36" s="22"/>
+      <c r="H36" s="96">
+        <v>134182.76</v>
+      </c>
+      <c r="I36" s="53"/>
+      <c r="K36" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A37" s="18"/>
+      <c r="B37" s="19"/>
+      <c r="C37" s="19"/>
+      <c r="D37" s="19"/>
+      <c r="E37" s="19"/>
+      <c r="F37" s="19"/>
+      <c r="G37" s="19"/>
+      <c r="H37" s="32"/>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A38" s="82" t="s">
+        <v>22</v>
+      </c>
+      <c r="B38" s="83"/>
+      <c r="C38" s="83"/>
+      <c r="D38" s="83"/>
+      <c r="E38" s="83"/>
+      <c r="F38" s="83"/>
+      <c r="G38" s="83"/>
+      <c r="H38" s="84"/>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A39" s="60" t="s">
+        <v>36</v>
+      </c>
+      <c r="B39" s="61"/>
+      <c r="C39" s="61"/>
+      <c r="D39" s="61"/>
+      <c r="E39" s="61"/>
+      <c r="F39" s="61"/>
+      <c r="G39" s="61"/>
+      <c r="H39" s="97">
+        <v>47532.32</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" s="16" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A40" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="B40" s="34"/>
+      <c r="C40" s="34"/>
+      <c r="D40" s="34"/>
+      <c r="E40" s="34"/>
+      <c r="F40" s="34"/>
+      <c r="G40" s="34"/>
+      <c r="H40" s="35">
+        <f>H18+H23+H27+H33+H36+H39</f>
+        <v>914065.58</v>
+      </c>
+      <c r="I40" s="62"/>
+    </row>
+    <row r="41" spans="1:12" s="14" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A41" s="55" t="s">
+        <v>39</v>
+      </c>
+      <c r="B41" s="56"/>
+      <c r="C41" s="56"/>
+      <c r="D41" s="56"/>
+      <c r="E41" s="56"/>
+      <c r="F41" s="56"/>
+      <c r="G41" s="56"/>
+      <c r="H41" s="57">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="72" t="s">
+        <v>14</v>
+      </c>
+      <c r="B42" s="73"/>
+      <c r="C42" s="73"/>
+      <c r="D42" s="73"/>
+      <c r="E42" s="73"/>
+      <c r="F42" s="73"/>
+      <c r="G42" s="73"/>
+      <c r="H42" s="74"/>
+    </row>
+    <row r="43" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="75"/>
+      <c r="B43" s="76"/>
+      <c r="C43" s="76"/>
+      <c r="D43" s="76"/>
+      <c r="E43" s="76"/>
+      <c r="F43" s="76"/>
+      <c r="G43" s="76"/>
+      <c r="H43" s="77"/>
+    </row>
+    <row r="44" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="68" t="s">
+        <v>54</v>
+      </c>
+      <c r="B44" s="69"/>
+      <c r="C44" s="69"/>
+      <c r="D44" s="69"/>
+      <c r="E44" s="69"/>
+      <c r="F44" s="69"/>
+      <c r="G44" s="69"/>
+      <c r="H44" s="36">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="92"/>
+      <c r="B45" s="93"/>
+      <c r="C45" s="93"/>
+      <c r="D45" s="93"/>
+      <c r="E45" s="93"/>
+      <c r="F45" s="93"/>
+      <c r="G45" s="94"/>
+      <c r="H45" s="36"/>
+    </row>
+    <row r="46" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="86"/>
+      <c r="B46" s="87"/>
+      <c r="C46" s="87"/>
+      <c r="D46" s="87"/>
+      <c r="E46" s="87"/>
+      <c r="F46" s="87"/>
+      <c r="G46" s="88"/>
+      <c r="H46" s="36"/>
+    </row>
+    <row r="47" spans="1:12" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="89" t="s">
+        <v>29</v>
+      </c>
+      <c r="B47" s="90"/>
+      <c r="C47" s="90"/>
+      <c r="D47" s="90"/>
+      <c r="E47" s="90"/>
+      <c r="F47" s="90"/>
+      <c r="G47" s="91"/>
+      <c r="H47" s="37">
+        <f>SUM(H44:H46)</f>
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A48" s="19"/>
+      <c r="B48" s="19"/>
+      <c r="C48" s="19"/>
+      <c r="D48" s="19"/>
+      <c r="E48" s="19"/>
+      <c r="F48" s="19"/>
+      <c r="G48" s="19"/>
+      <c r="H48" s="19"/>
+    </row>
+    <row r="49" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="65" t="s">
+        <v>42</v>
+      </c>
+      <c r="B49" s="66"/>
+      <c r="C49" s="66"/>
+      <c r="D49" s="66"/>
+      <c r="E49" s="66"/>
+      <c r="F49" s="66"/>
+      <c r="G49" s="67"/>
+      <c r="H49" s="64"/>
+    </row>
+    <row r="50" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="19"/>
+      <c r="B50" s="19"/>
+      <c r="C50" s="19"/>
+      <c r="D50" s="19"/>
+      <c r="E50" s="19"/>
+      <c r="F50" s="19"/>
+      <c r="G50" s="19"/>
+      <c r="H50" s="19"/>
+      <c r="J50" s="15"/>
+    </row>
+    <row r="51" spans="1:10" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="95" t="s">
+        <v>37</v>
+      </c>
+      <c r="B51" s="95"/>
+      <c r="C51" s="95"/>
+      <c r="D51" s="95"/>
+      <c r="E51" s="95"/>
+      <c r="F51" s="95"/>
+      <c r="G51" s="95"/>
+      <c r="H51" s="35">
+        <f>+H40+H41</f>
+        <v>1414065.58</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A52" s="38"/>
+      <c r="B52" s="38"/>
+      <c r="C52" s="38"/>
+      <c r="D52" s="38"/>
+      <c r="E52" s="38"/>
+      <c r="F52" s="38"/>
+      <c r="G52" s="38"/>
+      <c r="H52" s="39"/>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A53" s="19"/>
+      <c r="B53" s="19"/>
+      <c r="C53" s="19"/>
+      <c r="D53" s="19"/>
+      <c r="E53" s="19"/>
+      <c r="F53" s="19"/>
+      <c r="G53" s="19"/>
+      <c r="H53" s="19"/>
+    </row>
+    <row r="54" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A54" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="B54" s="34"/>
+      <c r="C54" s="34"/>
+      <c r="D54" s="34"/>
+      <c r="E54" s="34"/>
+      <c r="F54" s="34"/>
+      <c r="G54" s="34"/>
+      <c r="H54" s="40">
+        <f>H47</f>
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55" s="19"/>
+      <c r="B55" s="19"/>
+      <c r="C55" s="19"/>
+      <c r="D55" s="19"/>
+      <c r="E55" s="19"/>
+      <c r="F55" s="19"/>
+      <c r="G55" s="19"/>
+      <c r="H55" s="19"/>
+    </row>
+    <row r="56" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A56" s="78" t="s">
+        <v>15</v>
+      </c>
+      <c r="B56" s="79"/>
+      <c r="C56" s="79"/>
+      <c r="D56" s="79"/>
+      <c r="E56" s="79"/>
+      <c r="F56" s="79"/>
+      <c r="G56" s="79"/>
+      <c r="H56" s="80"/>
+    </row>
+    <row r="57" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A57" s="41" t="s">
+        <v>17</v>
+      </c>
+      <c r="B57" s="42"/>
+      <c r="C57" s="42"/>
+      <c r="D57" s="42"/>
+      <c r="E57" s="42"/>
+      <c r="F57" s="42"/>
+      <c r="G57" s="42"/>
+      <c r="H57" s="48">
+        <v>471114.10188048007</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="43" t="s">
         <v>48</v>
       </c>
-      <c r="B35" s="22"/>
-      <c r="C35" s="22"/>
-      <c r="D35" s="22"/>
-      <c r="E35" s="22"/>
-      <c r="F35" s="22"/>
-      <c r="G35" s="22"/>
-      <c r="H35" s="100">
-        <v>134182.76</v>
-      </c>
-      <c r="I35" s="53"/>
-      <c r="K35" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A36" s="18"/>
-      <c r="B36" s="19"/>
-      <c r="C36" s="19"/>
-      <c r="D36" s="19"/>
-      <c r="E36" s="19"/>
-      <c r="F36" s="19"/>
-      <c r="G36" s="19"/>
-      <c r="H36" s="32"/>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A37" s="82" t="s">
-        <v>22</v>
-      </c>
-      <c r="B37" s="83"/>
-      <c r="C37" s="83"/>
-      <c r="D37" s="83"/>
-      <c r="E37" s="83"/>
-      <c r="F37" s="83"/>
-      <c r="G37" s="83"/>
-      <c r="H37" s="84"/>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A38" s="60" t="s">
-        <v>36</v>
-      </c>
-      <c r="B38" s="61"/>
-      <c r="C38" s="61"/>
-      <c r="D38" s="61"/>
-      <c r="E38" s="61"/>
-      <c r="F38" s="61"/>
-      <c r="G38" s="61"/>
-      <c r="H38" s="99">
-        <v>47532.32</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" s="16" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="B39" s="34"/>
-      <c r="C39" s="34"/>
-      <c r="D39" s="34"/>
-      <c r="E39" s="34"/>
-      <c r="F39" s="34"/>
-      <c r="G39" s="34"/>
-      <c r="H39" s="35">
-        <f>H17+H22+H26+H32+H35+H38</f>
-        <v>856867.65</v>
-      </c>
-      <c r="I39" s="62"/>
-    </row>
-    <row r="40" spans="1:11" s="14" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="55" t="s">
-        <v>39</v>
-      </c>
-      <c r="B40" s="56"/>
-      <c r="C40" s="56"/>
-      <c r="D40" s="56"/>
-      <c r="E40" s="56"/>
-      <c r="F40" s="56"/>
-      <c r="G40" s="56"/>
-      <c r="H40" s="57"/>
-    </row>
-    <row r="41" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="72" t="s">
-        <v>14</v>
-      </c>
-      <c r="B41" s="73"/>
-      <c r="C41" s="73"/>
-      <c r="D41" s="73"/>
-      <c r="E41" s="73"/>
-      <c r="F41" s="73"/>
-      <c r="G41" s="73"/>
-      <c r="H41" s="74"/>
-    </row>
-    <row r="42" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="75"/>
-      <c r="B42" s="76"/>
-      <c r="C42" s="76"/>
-      <c r="D42" s="76"/>
-      <c r="E42" s="76"/>
-      <c r="F42" s="76"/>
-      <c r="G42" s="76"/>
-      <c r="H42" s="77"/>
-    </row>
-    <row r="43" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="68" t="s">
-        <v>43</v>
-      </c>
-      <c r="B43" s="69"/>
-      <c r="C43" s="69"/>
-      <c r="D43" s="69"/>
-      <c r="E43" s="69"/>
-      <c r="F43" s="69"/>
-      <c r="G43" s="69"/>
-      <c r="H43" s="36">
-        <v>420000</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="92"/>
-      <c r="B44" s="93"/>
-      <c r="C44" s="93"/>
-      <c r="D44" s="93"/>
-      <c r="E44" s="93"/>
-      <c r="F44" s="93"/>
-      <c r="G44" s="94"/>
-      <c r="H44" s="36"/>
-    </row>
-    <row r="45" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="86"/>
-      <c r="B45" s="87"/>
-      <c r="C45" s="87"/>
-      <c r="D45" s="87"/>
-      <c r="E45" s="87"/>
-      <c r="F45" s="87"/>
-      <c r="G45" s="88"/>
-      <c r="H45" s="36"/>
-    </row>
-    <row r="46" spans="1:11" s="14" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="89" t="s">
-        <v>29</v>
-      </c>
-      <c r="B46" s="90"/>
-      <c r="C46" s="90"/>
-      <c r="D46" s="90"/>
-      <c r="E46" s="90"/>
-      <c r="F46" s="90"/>
-      <c r="G46" s="91"/>
-      <c r="H46" s="37">
-        <f>SUM(H43:H45)</f>
-        <v>420000</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A47" s="19"/>
-      <c r="B47" s="19"/>
-      <c r="C47" s="19"/>
-      <c r="D47" s="19"/>
-      <c r="E47" s="19"/>
-      <c r="F47" s="19"/>
-      <c r="G47" s="19"/>
-      <c r="H47" s="19"/>
-    </row>
-    <row r="48" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="65" t="s">
-        <v>44</v>
-      </c>
-      <c r="B48" s="66"/>
-      <c r="C48" s="66"/>
-      <c r="D48" s="66"/>
-      <c r="E48" s="66"/>
-      <c r="F48" s="66"/>
-      <c r="G48" s="67"/>
-      <c r="H48" s="64"/>
-    </row>
-    <row r="49" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="19"/>
-      <c r="B49" s="19"/>
-      <c r="C49" s="19"/>
-      <c r="D49" s="19"/>
-      <c r="E49" s="19"/>
-      <c r="F49" s="19"/>
-      <c r="G49" s="19"/>
-      <c r="H49" s="19"/>
-      <c r="J49" s="15"/>
-    </row>
-    <row r="50" spans="1:10" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="95" t="s">
-        <v>37</v>
-      </c>
-      <c r="B50" s="95"/>
-      <c r="C50" s="95"/>
-      <c r="D50" s="95"/>
-      <c r="E50" s="95"/>
-      <c r="F50" s="95"/>
-      <c r="G50" s="95"/>
-      <c r="H50" s="35">
-        <f>+H39+H40</f>
-        <v>856867.65</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A51" s="38"/>
-      <c r="B51" s="38"/>
-      <c r="C51" s="38"/>
-      <c r="D51" s="38"/>
-      <c r="E51" s="38"/>
-      <c r="F51" s="38"/>
-      <c r="G51" s="38"/>
-      <c r="H51" s="39"/>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A52" s="19"/>
-      <c r="B52" s="19"/>
-      <c r="C52" s="19"/>
-      <c r="D52" s="19"/>
-      <c r="E52" s="19"/>
-      <c r="F52" s="19"/>
-      <c r="G52" s="19"/>
-      <c r="H52" s="19"/>
-    </row>
-    <row r="53" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A53" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="B53" s="34"/>
-      <c r="C53" s="34"/>
-      <c r="D53" s="34"/>
-      <c r="E53" s="34"/>
-      <c r="F53" s="34"/>
-      <c r="G53" s="34"/>
-      <c r="H53" s="40">
-        <f>H46</f>
-        <v>420000</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A54" s="19"/>
-      <c r="B54" s="19"/>
-      <c r="C54" s="19"/>
-      <c r="D54" s="19"/>
-      <c r="E54" s="19"/>
-      <c r="F54" s="19"/>
-      <c r="G54" s="19"/>
-      <c r="H54" s="19"/>
-    </row>
-    <row r="55" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A55" s="78" t="s">
-        <v>15</v>
-      </c>
-      <c r="B55" s="79"/>
-      <c r="C55" s="79"/>
-      <c r="D55" s="79"/>
-      <c r="E55" s="79"/>
-      <c r="F55" s="79"/>
-      <c r="G55" s="79"/>
-      <c r="H55" s="80"/>
-    </row>
-    <row r="56" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A56" s="41" t="s">
-        <v>17</v>
-      </c>
-      <c r="B56" s="42"/>
-      <c r="C56" s="42"/>
-      <c r="D56" s="42"/>
-      <c r="E56" s="42"/>
-      <c r="F56" s="42"/>
-      <c r="G56" s="42"/>
-      <c r="H56" s="48">
-        <v>596709.46716047998</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="43" t="s">
-        <v>50</v>
-      </c>
-      <c r="B57" s="44"/>
-      <c r="C57" s="44"/>
-      <c r="D57" s="44"/>
-      <c r="E57" s="44"/>
-      <c r="F57" s="44"/>
-      <c r="G57" s="44"/>
-      <c r="H57" s="54">
-        <v>995172.28472</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="43"/>
       <c r="B58" s="44"/>
       <c r="C58" s="44"/>
       <c r="D58" s="44"/>
       <c r="E58" s="44"/>
       <c r="F58" s="44"/>
       <c r="G58" s="44"/>
-      <c r="H58" s="49"/>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A59" s="43" t="s">
-        <v>35</v>
-      </c>
+      <c r="H58" s="54">
+        <v>1487196.277957391</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="43"/>
       <c r="B59" s="44"/>
       <c r="C59" s="44"/>
       <c r="D59" s="44"/>
@@ -1744,7 +1751,7 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="43" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="B60" s="44"/>
       <c r="C60" s="44"/>
@@ -1752,39 +1759,43 @@
       <c r="E60" s="44"/>
       <c r="F60" s="44"/>
       <c r="G60" s="44"/>
-      <c r="H60" s="45">
-        <f>-(H39+H53)</f>
-        <v>-1276867.6499999999</v>
-      </c>
-      <c r="J60" s="15"/>
-    </row>
-    <row r="61" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A61" s="46" t="s">
+      <c r="H60" s="49"/>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="B61" s="44"/>
+      <c r="C61" s="44"/>
+      <c r="D61" s="44"/>
+      <c r="E61" s="44"/>
+      <c r="F61" s="44"/>
+      <c r="G61" s="44"/>
+      <c r="H61" s="45">
+        <f>-(H40+H54)</f>
+        <v>-1364065.58</v>
+      </c>
+      <c r="J61" s="15"/>
+    </row>
+    <row r="62" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A62" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="B61" s="47"/>
-      <c r="C61" s="47"/>
-      <c r="D61" s="47"/>
-      <c r="E61" s="47"/>
-      <c r="F61" s="47"/>
-      <c r="G61" s="47"/>
-      <c r="H61" s="58">
-        <f>SUM(H56:H60)</f>
-        <v>315014.10188048007</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B63" s="70" t="s">
-        <v>49</v>
-      </c>
-      <c r="C63" s="70"/>
-      <c r="D63" s="70"/>
-      <c r="E63" s="70"/>
-      <c r="F63" s="70"/>
-      <c r="G63" s="70"/>
+      <c r="B62" s="47"/>
+      <c r="C62" s="47"/>
+      <c r="D62" s="47"/>
+      <c r="E62" s="47"/>
+      <c r="F62" s="47"/>
+      <c r="G62" s="47"/>
+      <c r="H62" s="58">
+        <f>SUM(H57:H61)</f>
+        <v>594244.79983787099</v>
+      </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B64" s="70"/>
+      <c r="B64" s="70" t="s">
+        <v>47</v>
+      </c>
       <c r="C64" s="70"/>
       <c r="D64" s="70"/>
       <c r="E64" s="70"/>
@@ -1839,24 +1850,32 @@
       <c r="F70" s="70"/>
       <c r="G70" s="70"/>
     </row>
+    <row r="71" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B71" s="70"/>
+      <c r="C71" s="70"/>
+      <c r="D71" s="70"/>
+      <c r="E71" s="70"/>
+      <c r="F71" s="70"/>
+      <c r="G71" s="70"/>
+    </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="B63:G70"/>
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="B64:G71"/>
     <mergeCell ref="E3:F3"/>
-    <mergeCell ref="A41:H42"/>
-    <mergeCell ref="A55:H55"/>
+    <mergeCell ref="A42:H43"/>
+    <mergeCell ref="A56:H56"/>
     <mergeCell ref="A12:H12"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A27:H27"/>
-    <mergeCell ref="A33:H33"/>
-    <mergeCell ref="A37:H37"/>
-    <mergeCell ref="A23:H23"/>
-    <mergeCell ref="A43:G43"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="A34:H34"/>
+    <mergeCell ref="A38:H38"/>
+    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="A44:G44"/>
+    <mergeCell ref="A46:G46"/>
+    <mergeCell ref="A47:G47"/>
     <mergeCell ref="A45:G45"/>
-    <mergeCell ref="A46:G46"/>
-    <mergeCell ref="A44:G44"/>
-    <mergeCell ref="A50:G50"/>
+    <mergeCell ref="A51:G51"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
